--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.14485932376638</v>
+        <v>9.123539640112037</v>
       </c>
       <c r="D2" t="n">
-        <v>55.78852586108322</v>
+        <v>9.065635452426022</v>
       </c>
       <c r="E2" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F2" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.79316002957734</v>
+        <v>8.416388504806317</v>
       </c>
       <c r="D3" t="n">
-        <v>51.52243727725116</v>
+        <v>8.372396057553315</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F3" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.17971430328394</v>
+        <v>9.291703574283641</v>
       </c>
       <c r="D4" t="n">
-        <v>57.02841809460602</v>
+        <v>9.267117940373479</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F4" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.07216116061959</v>
+        <v>7.649226188600684</v>
       </c>
       <c r="D5" t="n">
-        <v>46.37785288913301</v>
+        <v>7.536401094484114</v>
       </c>
       <c r="E5" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F5" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.35857671115429</v>
+        <v>6.720768715562571</v>
       </c>
       <c r="D6" t="n">
-        <v>40.75476444230166</v>
+        <v>6.62264922187402</v>
       </c>
       <c r="E6" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F6" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.36597978962541</v>
+        <v>1.034471715814129</v>
       </c>
       <c r="D7" t="n">
-        <v>5.679551316152645</v>
+        <v>0.9229270888748048</v>
       </c>
       <c r="E7" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F7" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>68.25022874707221</v>
+        <v>11.09066217139923</v>
       </c>
       <c r="D8" t="n">
-        <v>67.85253421807275</v>
+        <v>11.02603681043682</v>
       </c>
       <c r="E8" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F8" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.01083793367393</v>
+        <v>8.776761164222012</v>
       </c>
       <c r="D9" t="n">
-        <v>54.30925993600481</v>
+        <v>8.825254739600783</v>
       </c>
       <c r="E9" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F9" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.09541605412372</v>
+        <v>7.815505108795104</v>
       </c>
       <c r="D10" t="n">
-        <v>48.69310042812776</v>
+        <v>7.912628819570762</v>
       </c>
       <c r="E10" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F10" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.60871286366467</v>
+        <v>8.711415840345509</v>
       </c>
       <c r="D11" t="n">
-        <v>54.14652010924472</v>
+        <v>8.798809517752266</v>
       </c>
       <c r="E11" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F11" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>60.05985638324784</v>
+        <v>9.759726662277775</v>
       </c>
       <c r="D12" t="n">
-        <v>60.63799410125193</v>
+        <v>9.853674041453438</v>
       </c>
       <c r="E12" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F12" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>79.26458257283883</v>
+        <v>12.88049466808631</v>
       </c>
       <c r="D13" t="n">
-        <v>79.77176615357742</v>
+        <v>12.96291199995633</v>
       </c>
       <c r="E13" t="n">
-        <v>16.72884849069365</v>
+        <v>2.718437879737718</v>
       </c>
       <c r="F13" t="n">
-        <v>16.9838311753481</v>
+        <v>2.759872565994066</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
